--- a/Raccordoimmagini.xlsx
+++ b/Raccordoimmagini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1ebefe3ec78c491/Desktop/NauticaApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{0FF97FF9-AC23-4E43-9570-3A36D6A9F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4852B312-F9A6-4C6C-B698-105569AB94C1}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{0FF97FF9-AC23-4E43-9570-3A36D6A9F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B8C3B3E-951C-4FA2-9CD1-E5064232EE5C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43959177-43D3-4FF6-B28C-190D231F41AE}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>Figura</t>
   </si>
   <si>
-    <t>Progressivo</t>
-  </si>
-  <si>
     <t>1.1.1-10</t>
   </si>
   <si>
@@ -404,313 +401,316 @@
     <t>Immagine</t>
   </si>
   <si>
-    <t>Figura 1</t>
-  </si>
-  <si>
-    <t>Figura 2</t>
-  </si>
-  <si>
-    <t>Figura 3</t>
-  </si>
-  <si>
-    <t>Figura 4</t>
-  </si>
-  <si>
-    <t>Figura 5</t>
-  </si>
-  <si>
-    <t>Figura 6</t>
-  </si>
-  <si>
-    <t>Figura 7</t>
-  </si>
-  <si>
-    <t>Figura 8</t>
-  </si>
-  <si>
-    <t>Figura 9</t>
-  </si>
-  <si>
-    <t>Figura 10</t>
-  </si>
-  <si>
-    <t>Figura 11</t>
-  </si>
-  <si>
-    <t>Figura 12</t>
-  </si>
-  <si>
-    <t>Figura 13</t>
-  </si>
-  <si>
-    <t>Figura 14</t>
-  </si>
-  <si>
-    <t>Figura 15</t>
-  </si>
-  <si>
-    <t>Figura 16</t>
-  </si>
-  <si>
-    <t>Figura 17</t>
-  </si>
-  <si>
-    <t>Figura 18</t>
-  </si>
-  <si>
-    <t>Figura 19</t>
-  </si>
-  <si>
-    <t>Figura 20</t>
-  </si>
-  <si>
-    <t>Figura 21</t>
-  </si>
-  <si>
-    <t>Figura 22</t>
-  </si>
-  <si>
-    <t>Figura 23</t>
-  </si>
-  <si>
-    <t>Figura 24</t>
-  </si>
-  <si>
-    <t>Figura 25</t>
-  </si>
-  <si>
-    <t>Figura 26</t>
-  </si>
-  <si>
-    <t>Figura 27</t>
-  </si>
-  <si>
-    <t>Figura 28</t>
-  </si>
-  <si>
-    <t>Figura 29</t>
-  </si>
-  <si>
-    <t>Figura 30</t>
-  </si>
-  <si>
-    <t>Figura 31</t>
-  </si>
-  <si>
-    <t>Figura 32</t>
-  </si>
-  <si>
-    <t>Figura 33</t>
-  </si>
-  <si>
-    <t>Figura 34</t>
-  </si>
-  <si>
-    <t>Figura 35</t>
-  </si>
-  <si>
-    <t>Figura 36</t>
-  </si>
-  <si>
-    <t>Figura 37</t>
-  </si>
-  <si>
-    <t>Figura 38</t>
-  </si>
-  <si>
-    <t>Figura 39</t>
-  </si>
-  <si>
-    <t>Figura 40</t>
-  </si>
-  <si>
-    <t>Figura 41</t>
-  </si>
-  <si>
-    <t>Figura 42</t>
-  </si>
-  <si>
-    <t>Figura 43</t>
-  </si>
-  <si>
-    <t>Figura 44</t>
-  </si>
-  <si>
-    <t>Figura 45</t>
-  </si>
-  <si>
-    <t>Figura 46</t>
-  </si>
-  <si>
-    <t>Figura 47</t>
-  </si>
-  <si>
-    <t>Figura 48</t>
-  </si>
-  <si>
-    <t>Figura 49</t>
-  </si>
-  <si>
-    <t>Figura 50</t>
-  </si>
-  <si>
-    <t>Figura 51</t>
-  </si>
-  <si>
-    <t>Figura 52</t>
-  </si>
-  <si>
-    <t>Figura 53</t>
-  </si>
-  <si>
-    <t>Figura 54</t>
-  </si>
-  <si>
-    <t>Figura 55</t>
-  </si>
-  <si>
-    <t>Figura 56</t>
-  </si>
-  <si>
-    <t>Figura 57</t>
-  </si>
-  <si>
-    <t>Figura 58</t>
-  </si>
-  <si>
-    <t>Figura 59</t>
-  </si>
-  <si>
-    <t>Figura 60</t>
-  </si>
-  <si>
-    <t>Figura 61</t>
-  </si>
-  <si>
-    <t>Figura 62</t>
-  </si>
-  <si>
-    <t>Figura 63</t>
-  </si>
-  <si>
-    <t>Figura 64</t>
-  </si>
-  <si>
-    <t>Figura 65</t>
-  </si>
-  <si>
-    <t>Figura 66</t>
-  </si>
-  <si>
-    <t>Figura 67</t>
-  </si>
-  <si>
-    <t>Figura 68</t>
-  </si>
-  <si>
-    <t>Figura 69</t>
-  </si>
-  <si>
-    <t>Figura 70</t>
-  </si>
-  <si>
-    <t>Figura 71</t>
-  </si>
-  <si>
-    <t>Figura 72</t>
-  </si>
-  <si>
-    <t>Figura 73</t>
-  </si>
-  <si>
-    <t>Figura 74</t>
-  </si>
-  <si>
-    <t>Figura 75</t>
-  </si>
-  <si>
-    <t>Figura 76</t>
-  </si>
-  <si>
-    <t>Figura 77</t>
-  </si>
-  <si>
-    <t>Figura 78</t>
-  </si>
-  <si>
-    <t>Figura 79</t>
-  </si>
-  <si>
-    <t>Figura 80</t>
-  </si>
-  <si>
-    <t>Figura 81</t>
-  </si>
-  <si>
-    <t>Figura 82</t>
-  </si>
-  <si>
-    <t>Figura 83</t>
-  </si>
-  <si>
-    <t>Figura 84</t>
-  </si>
-  <si>
-    <t>Figura 85</t>
-  </si>
-  <si>
-    <t>Figura 86</t>
-  </si>
-  <si>
-    <t>Figura 87</t>
-  </si>
-  <si>
-    <t>Figura 88</t>
-  </si>
-  <si>
-    <t>Figura 89</t>
-  </si>
-  <si>
-    <t>Figura 90</t>
-  </si>
-  <si>
-    <t>Figura 91</t>
-  </si>
-  <si>
-    <t>Figura 92</t>
-  </si>
-  <si>
-    <t>Figura 93</t>
-  </si>
-  <si>
-    <t>Figura 94</t>
-  </si>
-  <si>
-    <t>Figura 95</t>
-  </si>
-  <si>
-    <t>Figura 96</t>
-  </si>
-  <si>
-    <t>Figura 97</t>
-  </si>
-  <si>
-    <t>Figura 98</t>
-  </si>
-  <si>
-    <t>Figura 99</t>
-  </si>
-  <si>
-    <t>Figura 100</t>
-  </si>
-  <si>
-    <t>Figura 101</t>
-  </si>
-  <si>
-    <t>Figura 102</t>
-  </si>
-  <si>
-    <t>Figura 103</t>
+    <t>ID Progressivo</t>
+  </si>
+  <si>
+    <t>Figura 1.png</t>
+  </si>
+  <si>
+    <t>Figura 2.png</t>
+  </si>
+  <si>
+    <t>Figura 3.png</t>
+  </si>
+  <si>
+    <t>Figura 4.png</t>
+  </si>
+  <si>
+    <t>Figura 5.png</t>
+  </si>
+  <si>
+    <t>Figura 6.png</t>
+  </si>
+  <si>
+    <t>Figura 7.png</t>
+  </si>
+  <si>
+    <t>Figura 8.png</t>
+  </si>
+  <si>
+    <t>Figura 9.png</t>
+  </si>
+  <si>
+    <t>Figura 10.png</t>
+  </si>
+  <si>
+    <t>Figura 11.png</t>
+  </si>
+  <si>
+    <t>Figura 12.png</t>
+  </si>
+  <si>
+    <t>Figura 13.png</t>
+  </si>
+  <si>
+    <t>Figura 14.png</t>
+  </si>
+  <si>
+    <t>Figura 15.png</t>
+  </si>
+  <si>
+    <t>Figura 16.png</t>
+  </si>
+  <si>
+    <t>Figura 17.png</t>
+  </si>
+  <si>
+    <t>Figura 18.png</t>
+  </si>
+  <si>
+    <t>Figura 19.png</t>
+  </si>
+  <si>
+    <t>Figura 20.png</t>
+  </si>
+  <si>
+    <t>Figura 21.png</t>
+  </si>
+  <si>
+    <t>Figura 22.png</t>
+  </si>
+  <si>
+    <t>Figura 23.png</t>
+  </si>
+  <si>
+    <t>Figura 24.png</t>
+  </si>
+  <si>
+    <t>Figura 25.png</t>
+  </si>
+  <si>
+    <t>Figura 26.png</t>
+  </si>
+  <si>
+    <t>Figura 27.png</t>
+  </si>
+  <si>
+    <t>Figura 28.png</t>
+  </si>
+  <si>
+    <t>Figura 29.png</t>
+  </si>
+  <si>
+    <t>Figura 30.png</t>
+  </si>
+  <si>
+    <t>Figura 31.png</t>
+  </si>
+  <si>
+    <t>Figura 32.png</t>
+  </si>
+  <si>
+    <t>Figura 33.png</t>
+  </si>
+  <si>
+    <t>Figura 34.png</t>
+  </si>
+  <si>
+    <t>Figura 35.png</t>
+  </si>
+  <si>
+    <t>Figura 36.png</t>
+  </si>
+  <si>
+    <t>Figura 37.png</t>
+  </si>
+  <si>
+    <t>Figura 38.png</t>
+  </si>
+  <si>
+    <t>Figura 39.png</t>
+  </si>
+  <si>
+    <t>Figura 40.png</t>
+  </si>
+  <si>
+    <t>Figura 41.png</t>
+  </si>
+  <si>
+    <t>Figura 42.png</t>
+  </si>
+  <si>
+    <t>Figura 43.png</t>
+  </si>
+  <si>
+    <t>Figura 44.png</t>
+  </si>
+  <si>
+    <t>Figura 45.png</t>
+  </si>
+  <si>
+    <t>Figura 46.png</t>
+  </si>
+  <si>
+    <t>Figura 47.png</t>
+  </si>
+  <si>
+    <t>Figura 48.png</t>
+  </si>
+  <si>
+    <t>Figura 49.png</t>
+  </si>
+  <si>
+    <t>Figura 50.png</t>
+  </si>
+  <si>
+    <t>Figura 51.png</t>
+  </si>
+  <si>
+    <t>Figura 52.png</t>
+  </si>
+  <si>
+    <t>Figura 53.png</t>
+  </si>
+  <si>
+    <t>Figura 54.png</t>
+  </si>
+  <si>
+    <t>Figura 55.png</t>
+  </si>
+  <si>
+    <t>Figura 56.png</t>
+  </si>
+  <si>
+    <t>Figura 57.png</t>
+  </si>
+  <si>
+    <t>Figura 58.png</t>
+  </si>
+  <si>
+    <t>Figura 59.png</t>
+  </si>
+  <si>
+    <t>Figura 60.png</t>
+  </si>
+  <si>
+    <t>Figura 61.png</t>
+  </si>
+  <si>
+    <t>Figura 62.png</t>
+  </si>
+  <si>
+    <t>Figura 63.png</t>
+  </si>
+  <si>
+    <t>Figura 64.png</t>
+  </si>
+  <si>
+    <t>Figura 65.png</t>
+  </si>
+  <si>
+    <t>Figura 66.png</t>
+  </si>
+  <si>
+    <t>Figura 67.png</t>
+  </si>
+  <si>
+    <t>Figura 68.png</t>
+  </si>
+  <si>
+    <t>Figura 69.png</t>
+  </si>
+  <si>
+    <t>Figura 70.png</t>
+  </si>
+  <si>
+    <t>Figura 71.png</t>
+  </si>
+  <si>
+    <t>Figura 72.png</t>
+  </si>
+  <si>
+    <t>Figura 73.png</t>
+  </si>
+  <si>
+    <t>Figura 74.png</t>
+  </si>
+  <si>
+    <t>Figura 75.png</t>
+  </si>
+  <si>
+    <t>Figura 76.png</t>
+  </si>
+  <si>
+    <t>Figura 77.png</t>
+  </si>
+  <si>
+    <t>Figura 78.png</t>
+  </si>
+  <si>
+    <t>Figura 79.png</t>
+  </si>
+  <si>
+    <t>Figura 80.png</t>
+  </si>
+  <si>
+    <t>Figura 81.png</t>
+  </si>
+  <si>
+    <t>Figura 82.png</t>
+  </si>
+  <si>
+    <t>Figura 83.png</t>
+  </si>
+  <si>
+    <t>Figura 84.png</t>
+  </si>
+  <si>
+    <t>Figura 85.png</t>
+  </si>
+  <si>
+    <t>Figura 86.png</t>
+  </si>
+  <si>
+    <t>Figura 87.png</t>
+  </si>
+  <si>
+    <t>Figura 88.png</t>
+  </si>
+  <si>
+    <t>Figura 89.png</t>
+  </si>
+  <si>
+    <t>Figura 90.png</t>
+  </si>
+  <si>
+    <t>Figura 91.png</t>
+  </si>
+  <si>
+    <t>Figura 92.png</t>
+  </si>
+  <si>
+    <t>Figura 93.png</t>
+  </si>
+  <si>
+    <t>Figura 94.png</t>
+  </si>
+  <si>
+    <t>Figura 95.png</t>
+  </si>
+  <si>
+    <t>Figura 96.png</t>
+  </si>
+  <si>
+    <t>Figura 97.png</t>
+  </si>
+  <si>
+    <t>Figura 98.png</t>
+  </si>
+  <si>
+    <t>Figura 99.png</t>
+  </si>
+  <si>
+    <t>Figura 100.png</t>
+  </si>
+  <si>
+    <t>Figura 101.png</t>
+  </si>
+  <si>
+    <t>Figura 102.png</t>
+  </si>
+  <si>
+    <t>Figura 103.png</t>
   </si>
 </sst>
 </file>
@@ -1112,18 +1112,18 @@
   <dimension ref="A1:C120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1131,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>122</v>
@@ -1142,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>123</v>
@@ -1153,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>124</v>
@@ -1164,7 +1164,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>125</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>126</v>
@@ -1186,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>127</v>
@@ -1197,7 +1197,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>128</v>
@@ -1208,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>129</v>
@@ -1219,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>130</v>
@@ -1230,7 +1230,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
         <v>131</v>
@@ -1241,7 +1241,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>132</v>
@@ -1252,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>133</v>
@@ -1263,7 +1263,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>134</v>
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>135</v>
@@ -1285,7 +1285,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>136</v>
@@ -1296,7 +1296,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>137</v>
@@ -1307,7 +1307,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>138</v>
@@ -1318,7 +1318,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>139</v>
@@ -1329,7 +1329,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>140</v>
@@ -1340,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>141</v>
@@ -1351,7 +1351,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>142</v>
@@ -1362,7 +1362,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>143</v>
@@ -1373,7 +1373,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -1384,7 +1384,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>145</v>
@@ -1395,7 +1395,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>146</v>
@@ -1406,7 +1406,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>147</v>
@@ -1417,7 +1417,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>147</v>
@@ -1428,7 +1428,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>148</v>
@@ -1439,7 +1439,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
         <v>149</v>
@@ -1450,7 +1450,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>150</v>
@@ -1461,7 +1461,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
         <v>151</v>
@@ -1472,7 +1472,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
         <v>152</v>
@@ -1483,7 +1483,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
         <v>152</v>
@@ -1494,7 +1494,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
         <v>153</v>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
         <v>153</v>
@@ -1516,7 +1516,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
         <v>154</v>
@@ -1527,7 +1527,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
         <v>155</v>
@@ -1538,7 +1538,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
         <v>156</v>
@@ -1549,7 +1549,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
         <v>157</v>
@@ -1560,7 +1560,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
         <v>158</v>
@@ -1571,7 +1571,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
         <v>159</v>
@@ -1582,7 +1582,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
         <v>160</v>
@@ -1593,7 +1593,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
         <v>161</v>
@@ -1604,7 +1604,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
         <v>162</v>
@@ -1615,7 +1615,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
         <v>163</v>
@@ -1626,7 +1626,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
         <v>164</v>
@@ -1637,7 +1637,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
         <v>165</v>
@@ -1648,7 +1648,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
         <v>166</v>
@@ -1659,7 +1659,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
         <v>167</v>
@@ -1670,7 +1670,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
         <v>168</v>
@@ -1681,7 +1681,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
         <v>169</v>
@@ -1692,7 +1692,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
         <v>170</v>
@@ -1703,7 +1703,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
         <v>171</v>
@@ -1714,7 +1714,7 @@
         <v>51</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
         <v>172</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
         <v>173</v>
@@ -1736,7 +1736,7 @@
         <v>53</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
         <v>174</v>
@@ -1747,7 +1747,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" t="s">
         <v>175</v>
@@ -1758,7 +1758,7 @@
         <v>55</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
         <v>176</v>
@@ -1769,7 +1769,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" t="s">
         <v>177</v>
@@ -1780,7 +1780,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s">
         <v>178</v>
@@ -1791,7 +1791,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" t="s">
         <v>179</v>
@@ -1802,7 +1802,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
         <v>180</v>
@@ -1813,7 +1813,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" t="s">
         <v>181</v>
@@ -1824,7 +1824,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C65" t="s">
         <v>182</v>
@@ -1835,7 +1835,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" t="s">
         <v>183</v>
@@ -1846,7 +1846,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
         <v>184</v>
@@ -1857,7 +1857,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" t="s">
         <v>185</v>
@@ -1868,7 +1868,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
         <v>186</v>
@@ -1879,7 +1879,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C70" t="s">
         <v>187</v>
@@ -1890,7 +1890,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C71" t="s">
         <v>188</v>
@@ -1901,7 +1901,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" t="s">
         <v>188</v>
@@ -1912,7 +1912,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C73" t="s">
         <v>188</v>
@@ -1923,7 +1923,7 @@
         <v>68</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C74" t="s">
         <v>189</v>
@@ -1934,7 +1934,7 @@
         <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C75" t="s">
         <v>189</v>
@@ -1945,7 +1945,7 @@
         <v>68</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" t="s">
         <v>189</v>
@@ -1956,7 +1956,7 @@
         <v>69</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C77" t="s">
         <v>190</v>
@@ -1967,7 +1967,7 @@
         <v>69</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C78" t="s">
         <v>190</v>
@@ -1978,7 +1978,7 @@
         <v>69</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C79" t="s">
         <v>190</v>
@@ -1989,7 +1989,7 @@
         <v>70</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C80" t="s">
         <v>191</v>
@@ -2000,7 +2000,7 @@
         <v>71</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C81" t="s">
         <v>192</v>
@@ -2011,7 +2011,7 @@
         <v>72</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C82" t="s">
         <v>193</v>
@@ -2022,7 +2022,7 @@
         <v>73</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C83" t="s">
         <v>194</v>
@@ -2033,7 +2033,7 @@
         <v>74</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" t="s">
         <v>195</v>
@@ -2044,7 +2044,7 @@
         <v>75</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
         <v>196</v>
@@ -2055,7 +2055,7 @@
         <v>76</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
         <v>197</v>
@@ -2066,7 +2066,7 @@
         <v>76</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
         <v>197</v>
@@ -2077,7 +2077,7 @@
         <v>77</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
         <v>198</v>
@@ -2088,7 +2088,7 @@
         <v>78</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C89" t="s">
         <v>199</v>
@@ -2099,7 +2099,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C90" t="s">
         <v>199</v>
@@ -2110,7 +2110,7 @@
         <v>78</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C91" t="s">
         <v>199</v>
@@ -2121,7 +2121,7 @@
         <v>79</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C92" t="s">
         <v>200</v>
@@ -2132,7 +2132,7 @@
         <v>79</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
         <v>200</v>
@@ -2143,7 +2143,7 @@
         <v>80</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C94" t="s">
         <v>201</v>
@@ -2154,7 +2154,7 @@
         <v>80</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C95" t="s">
         <v>201</v>
@@ -2165,7 +2165,7 @@
         <v>80</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C96" t="s">
         <v>201</v>
@@ -2176,7 +2176,7 @@
         <v>81</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C97" t="s">
         <v>202</v>
@@ -2187,7 +2187,7 @@
         <v>81</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C98" t="s">
         <v>202</v>
@@ -2198,7 +2198,7 @@
         <v>82</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C99" t="s">
         <v>203</v>
@@ -2209,7 +2209,7 @@
         <v>83</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C100" t="s">
         <v>204</v>
@@ -2220,7 +2220,7 @@
         <v>84</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C101" t="s">
         <v>205</v>
@@ -2231,7 +2231,7 @@
         <v>85</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C102" t="s">
         <v>206</v>
@@ -2242,7 +2242,7 @@
         <v>86</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C103" t="s">
         <v>207</v>
@@ -2253,7 +2253,7 @@
         <v>87</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C104" t="s">
         <v>208</v>
@@ -2264,7 +2264,7 @@
         <v>88</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C105" t="s">
         <v>209</v>
@@ -2275,7 +2275,7 @@
         <v>89</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C106" t="s">
         <v>210</v>
@@ -2286,7 +2286,7 @@
         <v>90</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C107" t="s">
         <v>211</v>
@@ -2297,7 +2297,7 @@
         <v>91</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" t="s">
         <v>212</v>
@@ -2308,7 +2308,7 @@
         <v>92</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C109" t="s">
         <v>213</v>
@@ -2319,7 +2319,7 @@
         <v>93</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C110" t="s">
         <v>214</v>
@@ -2330,7 +2330,7 @@
         <v>94</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C111" t="s">
         <v>215</v>
@@ -2341,7 +2341,7 @@
         <v>95</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C112" t="s">
         <v>216</v>
@@ -2352,7 +2352,7 @@
         <v>96</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C113" t="s">
         <v>217</v>
@@ -2363,7 +2363,7 @@
         <v>97</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C114" t="s">
         <v>218</v>
@@ -2374,7 +2374,7 @@
         <v>98</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C115" t="s">
         <v>219</v>
@@ -2385,7 +2385,7 @@
         <v>99</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C116" t="s">
         <v>220</v>
@@ -2396,7 +2396,7 @@
         <v>100</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C117" t="s">
         <v>221</v>
@@ -2407,7 +2407,7 @@
         <v>101</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C118" t="s">
         <v>222</v>
@@ -2418,7 +2418,7 @@
         <v>102</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s">
         <v>223</v>
@@ -2429,7 +2429,7 @@
         <v>103</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s">
         <v>224</v>
